--- a/resources/templates/standard/J1100-07.xlsx
+++ b/resources/templates/standard/J1100-07.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="44">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>TRY-OUT 완료 보고서</t>
   </si>
@@ -821,12 +824,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -841,18 +846,18 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
       <c r="R1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T1" s="4"/>
       <c r="U1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V1" s="4"/>
       <c r="W1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X1" s="4"/>
     </row>
@@ -936,7 +941,7 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -950,7 +955,7 @@
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
       <c r="M5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
@@ -966,7 +971,7 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
@@ -980,7 +985,7 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
@@ -996,7 +1001,7 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -1010,7 +1015,7 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
@@ -1026,13 +1031,13 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
@@ -1040,20 +1045,20 @@
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
       <c r="K8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" s="12" t="s">
         <v>13</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>12</v>
       </c>
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
       <c r="P8" s="12"/>
       <c r="Q8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="R8" s="12" t="s">
         <v>13</v>
-      </c>
-      <c r="R8" s="12" t="s">
-        <v>12</v>
       </c>
       <c r="S8" s="12"/>
       <c r="T8" s="12"/>
@@ -1061,7 +1066,7 @@
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
       <c r="X8" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
@@ -1118,45 +1123,45 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
       <c r="H11" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" s="12"/>
       <c r="J11" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="12"/>
       <c r="M11" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" s="12"/>
       <c r="O11" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
       <c r="R11" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S11" s="12"/>
       <c r="T11" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U11" s="12"/>
       <c r="V11" s="12"/>
       <c r="W11" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X11" s="12"/>
     </row>
@@ -1292,7 +1297,7 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -1320,13 +1325,13 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
@@ -1343,7 +1348,7 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
@@ -1794,7 +1799,7 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
@@ -1822,10 +1827,10 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C37" s="31"/>
       <c r="D37" s="31"/>
@@ -1835,7 +1840,7 @@
       <c r="H37" s="31"/>
       <c r="I37" s="31"/>
       <c r="J37" s="30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K37" s="31"/>
       <c r="L37" s="31"/>
@@ -1845,13 +1850,13 @@
       <c r="P37" s="31"/>
       <c r="Q37" s="32"/>
       <c r="R37" s="30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S37" s="31"/>
       <c r="T37" s="31"/>
       <c r="U37" s="32"/>
       <c r="V37" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W37" s="31"/>
       <c r="X37" s="33"/>
@@ -2300,7 +2305,7 @@
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -2328,10 +2333,10 @@
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C56" s="36"/>
       <c r="D56" s="36"/>
@@ -2343,7 +2348,7 @@
       <c r="J56" s="36"/>
       <c r="K56" s="36"/>
       <c r="L56" s="36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M56" s="36"/>
       <c r="N56" s="36"/>
@@ -2353,7 +2358,7 @@
       <c r="R56" s="36"/>
       <c r="S56" s="36"/>
       <c r="T56" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
@@ -2365,7 +2370,7 @@
         <v>1</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
@@ -2377,7 +2382,7 @@
       <c r="J57" s="11"/>
       <c r="K57" s="11"/>
       <c r="L57" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M57" s="11"/>
       <c r="N57" s="11"/>
@@ -2397,7 +2402,7 @@
         <v>2</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
@@ -2409,7 +2414,7 @@
       <c r="J58" s="11"/>
       <c r="K58" s="11"/>
       <c r="L58" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M58" s="11"/>
       <c r="N58" s="11"/>
@@ -2429,7 +2434,7 @@
         <v>3</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
@@ -2441,7 +2446,7 @@
       <c r="J59" s="11"/>
       <c r="K59" s="11"/>
       <c r="L59" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M59" s="11"/>
       <c r="N59" s="11"/>
@@ -2461,7 +2466,7 @@
         <v>4</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
@@ -2473,7 +2478,7 @@
       <c r="J60" s="11"/>
       <c r="K60" s="11"/>
       <c r="L60" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M60" s="11"/>
       <c r="N60" s="11"/>
@@ -2493,7 +2498,7 @@
         <v>5</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
@@ -2505,7 +2510,7 @@
       <c r="J61" s="11"/>
       <c r="K61" s="11"/>
       <c r="L61" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M61" s="11"/>
       <c r="N61" s="11"/>
@@ -2525,7 +2530,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
@@ -2537,7 +2542,7 @@
       <c r="J62" s="11"/>
       <c r="K62" s="11"/>
       <c r="L62" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M62" s="11"/>
       <c r="N62" s="11"/>
@@ -2557,7 +2562,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
@@ -2569,7 +2574,7 @@
       <c r="J63" s="11"/>
       <c r="K63" s="11"/>
       <c r="L63" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M63" s="11"/>
       <c r="N63" s="11"/>
@@ -2589,7 +2594,7 @@
         <v>8</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
@@ -2601,7 +2606,7 @@
       <c r="J64" s="11"/>
       <c r="K64" s="11"/>
       <c r="L64" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M64" s="11"/>
       <c r="N64" s="11"/>
@@ -2621,7 +2626,7 @@
         <v>9</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
@@ -2633,7 +2638,7 @@
       <c r="J65" s="11"/>
       <c r="K65" s="11"/>
       <c r="L65" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M65" s="11"/>
       <c r="N65" s="11"/>
